--- a/metrics/metricas.xlsx
+++ b/metrics/metricas.xlsx
@@ -41,12 +41,17 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -73,21 +78,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -96,8 +104,303 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Hoja 1'!$E$3:$E$6</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Hoja 1'!$E$3:$E$6</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4A86E8"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Hoja 1'!$E$3:$E$6</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Hoja 1'!$G$3:$G$6</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1057451796"/>
+        <c:axId val="721799027"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1057451796"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="721799027"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="721799027"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0" sz="1400">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="1400">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>tiempo </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1057451796"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6019800" cy="3714750"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 1" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -305,7 +608,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="13.75"/>
+    <col customWidth="1" min="3" max="3" width="22.25"/>
     <col customWidth="1" min="6" max="6" width="23.13"/>
     <col customWidth="1" min="7" max="7" width="22.75"/>
   </cols>
@@ -320,293 +623,311 @@
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>1000000.0</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>74.0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>1.0</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>2557.0</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <v>2684.0</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <f t="shared" ref="H3:H13" si="1">F3/G3</f>
         <v>0.9526825633</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="6">
         <f t="shared" ref="I3:I13" si="2">H3/E3</f>
         <v>0.9526825633</v>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>1000000.0</v>
       </c>
-      <c r="D4" s="3">
-        <v>2488.0</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="D4" s="4">
+        <v>74.0</v>
+      </c>
+      <c r="E4" s="4">
         <v>2.0</v>
       </c>
-      <c r="F4" s="3">
-        <v>2741.0</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="F4" s="4">
+        <v>2557.0</v>
+      </c>
+      <c r="G4" s="4">
         <v>1062.0</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <f t="shared" si="1"/>
-        <v>2.580979284</v>
-      </c>
-      <c r="I4" s="5">
+        <v>2.407721281</v>
+      </c>
+      <c r="I4" s="6">
         <f t="shared" si="2"/>
-        <v>1.290489642</v>
+        <v>1.20386064</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>1000000.0</v>
       </c>
-      <c r="D5" s="3">
-        <v>784.0</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D5" s="4">
+        <v>74.0</v>
+      </c>
+      <c r="E5" s="4">
         <v>4.0</v>
       </c>
-      <c r="F5" s="3">
-        <v>2846.0</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="F5" s="4">
+        <v>2557.0</v>
+      </c>
+      <c r="G5" s="4">
         <v>710.0</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="5">
         <f t="shared" si="1"/>
-        <v>4.008450704</v>
-      </c>
-      <c r="I5" s="5">
+        <v>3.601408451</v>
+      </c>
+      <c r="I5" s="6">
         <f t="shared" si="2"/>
-        <v>1.002112676</v>
+        <v>0.9003521127</v>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>1000000.0</v>
       </c>
-      <c r="D6" s="3">
-        <v>4866.0</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="D6" s="4">
+        <v>74.0</v>
+      </c>
+      <c r="E6" s="4">
         <v>8.0</v>
       </c>
-      <c r="F6" s="3">
-        <v>2778.0</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="F6" s="4">
+        <v>2557.0</v>
+      </c>
+      <c r="G6" s="4">
         <v>713.0</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <f t="shared" si="1"/>
-        <v>3.896213184</v>
-      </c>
-      <c r="I6" s="5">
+        <v>3.586255259</v>
+      </c>
+      <c r="I6" s="6">
         <f t="shared" si="2"/>
-        <v>0.487026648</v>
+        <v>0.4482819074</v>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>1.0E7</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>4987.0</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>1.0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>3489.0</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <v>3669.0</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="5">
         <f t="shared" si="1"/>
         <v>0.9509403107</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="6">
         <f t="shared" si="2"/>
         <v>0.9509403107</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>1.0E7</v>
       </c>
-      <c r="D8" s="3">
-        <v>87.0</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="4">
+        <v>4987.0</v>
+      </c>
+      <c r="E8" s="4">
         <v>2.0</v>
       </c>
-      <c r="F8" s="3">
-        <v>2847.0</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F8" s="4">
+        <v>3489.0</v>
+      </c>
+      <c r="G8" s="4">
         <v>2339.0</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <f t="shared" si="1"/>
-        <v>1.217186832</v>
-      </c>
-      <c r="I8" s="5">
+        <v>1.491663104</v>
+      </c>
+      <c r="I8" s="6">
         <f t="shared" si="2"/>
-        <v>0.608593416</v>
+        <v>0.7458315519</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>1.0E7</v>
       </c>
-      <c r="D9" s="3">
-        <v>634.0</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="4">
+        <v>4987.0</v>
+      </c>
+      <c r="E9" s="4">
         <v>4.0</v>
       </c>
-      <c r="F9" s="3">
-        <v>3249.0</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="F9" s="4">
+        <v>3489.0</v>
+      </c>
+      <c r="G9" s="4">
         <v>1933.0</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <f t="shared" si="1"/>
-        <v>1.680807036</v>
-      </c>
-      <c r="I9" s="5">
+        <v>1.804966374</v>
+      </c>
+      <c r="I9" s="6">
         <f t="shared" si="2"/>
-        <v>0.4202017589</v>
+        <v>0.4512415934</v>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>1.0E7</v>
       </c>
-      <c r="D10" s="3">
-        <v>987.0</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="4">
+        <v>4987.0</v>
+      </c>
+      <c r="E10" s="4">
         <v>8.0</v>
       </c>
-      <c r="F10" s="3">
-        <v>3541.0</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="F10" s="4">
+        <v>3489.0</v>
+      </c>
+      <c r="G10" s="4">
         <v>2446.0</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="5">
         <f t="shared" si="1"/>
-        <v>1.447669665</v>
-      </c>
-      <c r="I10" s="5">
+        <v>1.426410466</v>
+      </c>
+      <c r="I10" s="6">
         <f t="shared" si="2"/>
-        <v>0.1809587081</v>
+        <v>0.1783013083</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>1.0E7</v>
       </c>
-      <c r="D11" s="3">
-        <v>784.0</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="D11" s="4">
+        <v>4987.0</v>
+      </c>
+      <c r="E11" s="4">
         <v>8.0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>31968.0</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <v>8796.0</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <f t="shared" si="1"/>
         <v>3.634379263</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="6">
         <f t="shared" si="2"/>
         <v>0.4542974079</v>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>475400.0</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>7844.0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>8.0</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>337.0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>188.0</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <f t="shared" si="1"/>
         <v>1.792553191</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="6">
         <f t="shared" si="2"/>
         <v>0.2240691489</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>1000000.0</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>477.0</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="4">
         <v>8.0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <v>1357.0</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="4">
         <v>469.0</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="5">
         <f t="shared" si="1"/>
         <v>2.893390192</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="6">
         <f t="shared" si="2"/>
         <v>0.361673774</v>
       </c>
+    </row>
+    <row r="16">
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
